--- a/data/trans_orig/P16A_n_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P16A_n_R-Habitat-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según número de medicamentos consumidos por persona en las dos últimas semanas</t>
+          <t>Población según número de medicamentos consumidos por persona en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,12 +716,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,62; 0,78</t>
+          <t>0,62; 0,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,95; 1,16</t>
+          <t>0,95; 1,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -731,47 +731,47 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,26; 1,56</t>
+          <t>1,25; 1,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 1,08</t>
+          <t>0,91; 1,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,49; 1,79</t>
+          <t>1,52; 1,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,38; 1,64</t>
+          <t>1,39; 1,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,35; 1,92</t>
+          <t>1,35; 1,91</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,78; 0,9</t>
+          <t>0,79; 0,91</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,25; 1,44</t>
+          <t>1,26; 1,45</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,14; 1,3</t>
+          <t>1,15; 1,31</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 1,7</t>
+          <t>1,42; 1,71</t>
         </is>
       </c>
     </row>
@@ -861,37 +861,37 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,89; 1,07</t>
+          <t>0,88; 1,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 0,99</t>
+          <t>0,85; 1,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,13</t>
+          <t>0,4; 1,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,04; 1,21</t>
+          <t>1,05; 1,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,5; 1,73</t>
+          <t>1,49; 1,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,23; 1,43</t>
+          <t>1,24; 1,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,62; 1,83</t>
+          <t>1,6; 1,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 1,38</t>
+          <t>1,23; 1,38</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,59; 0,77</t>
+          <t>0,6; 0,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 1,07</t>
+          <t>0,84; 1,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1011,27 +1011,27 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,09; 1,36</t>
+          <t>1,1; 1,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 1,34</t>
+          <t>1,11; 1,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,37; 1,61</t>
+          <t>1,37; 1,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,18; 1,43</t>
+          <t>1,19; 1,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,45; 2,94</t>
+          <t>1,44; 3,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1041,17 +1041,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,14; 1,31</t>
+          <t>1,15; 1,31</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 1,17</t>
+          <t>1,01; 1,18</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,33; 2,49</t>
+          <t>1,33; 2,44</t>
         </is>
       </c>
     </row>
@@ -1146,42 +1146,42 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,87; 1,02</t>
+          <t>0,87; 1,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 1,41</t>
+          <t>1,2; 1,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,12; 1,31</t>
+          <t>1,11; 1,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,61; 1,85</t>
+          <t>1,6; 1,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,35; 1,57</t>
+          <t>1,36; 1,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,66; 1,95</t>
+          <t>1,67; 1,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,92; 1,05</t>
+          <t>0,93; 1,05</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,34; 1,5</t>
+          <t>1,35; 1,52</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,5; 1,68</t>
+          <t>1,49; 1,67</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,68; 0,75</t>
+          <t>0,68; 0,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1286,17 +1286,17 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,88; 0,96</t>
+          <t>0,87; 0,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 1,27</t>
+          <t>0,89; 1,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,09; 1,19</t>
+          <t>1,1; 1,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1306,12 +1306,12 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,33; 1,45</t>
+          <t>1,34; 1,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,68; 2,25</t>
+          <t>1,69; 2,24</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,29; 1,36</t>
+          <t>1,29; 1,37</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,37; 1,75</t>
+          <t>1,38; 1,71</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A_n_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P16A_n_R-Habitat-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,4</t>
+          <t>1,39</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,74</t>
+          <t>1,84</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,58</t>
+          <t>1,62</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,95; 1,15</t>
+          <t>0,94; 1,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,84; 1,05</t>
+          <t>0,84; 1,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,25; 1,56</t>
+          <t>1,24; 1,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -741,27 +741,27 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,52; 1,79</t>
+          <t>1,5; 1,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,39; 1,64</t>
+          <t>1,37; 1,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,35; 1,91</t>
+          <t>1,71; 1,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,79; 0,91</t>
+          <t>0,78; 0,91</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,26; 1,45</t>
+          <t>1,25; 1,42</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 1,71</t>
+          <t>1,53; 1,72</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,87</t>
+          <t>1,08</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,71</t>
+          <t>1,69</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,24</t>
+          <t>1,39</t>
         </is>
       </c>
     </row>
@@ -856,12 +856,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 0,82</t>
+          <t>0,67; 0,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 1,05</t>
+          <t>0,89; 1,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,12</t>
+          <t>0,98; 1,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,49; 1,75</t>
+          <t>1,5; 1,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -891,17 +891,17 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,6; 1,81</t>
+          <t>1,59; 1,8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 1,0</t>
+          <t>0,88; 0,99</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,23; 1,38</t>
+          <t>1,22; 1,37</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,85; 1,43</t>
+          <t>1,31; 1,46</t>
         </is>
       </c>
     </row>
@@ -943,39 +943,39 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>1,22</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1,48</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1,3</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1,56</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0,94</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>1,22</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,48</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,3</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2,06</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0,94</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>1,22</t>
-        </is>
-      </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
           <t>1,09</t>
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,7</t>
+          <t>1,38</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 0,77</t>
+          <t>0,59; 0,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 1,08</t>
+          <t>0,85; 1,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1011,47 +1011,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 1,34</t>
+          <t>1,09; 1,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,11; 1,34</t>
+          <t>1,09; 1,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,37; 1,6</t>
+          <t>1,37; 1,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,19; 1,43</t>
+          <t>1,2; 1,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,04</t>
+          <t>1,43; 1,68</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 1,02</t>
+          <t>0,88; 1,02</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 1,31</t>
+          <t>1,14; 1,3</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 1,18</t>
+          <t>1,01; 1,17</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,33; 2,44</t>
+          <t>1,29; 1,47</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,3</t>
+          <t>1,27</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,83</t>
+          <t>1,85</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,59</t>
+          <t>1,58</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,99; 1,22</t>
+          <t>0,99; 1,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1151,32 +1151,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,2; 1,41</t>
+          <t>1,17; 1,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,11; 1,29</t>
+          <t>1,12; 1,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,6; 1,84</t>
+          <t>1,6; 1,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,36; 1,58</t>
+          <t>1,35; 1,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,67; 1,97</t>
+          <t>1,74; 1,98</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 1,05</t>
+          <t>0,92; 1,05</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,49; 1,67</t>
+          <t>1,5; 1,66</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,15</t>
+          <t>1,22</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,84</t>
+          <t>1,74</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,51</t>
+          <t>1,49</t>
         </is>
       </c>
     </row>
@@ -1281,22 +1281,22 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,96; 1,07</t>
+          <t>0,97; 1,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 0,96</t>
+          <t>0,88; 0,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 1,26</t>
+          <t>1,17; 1,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,1; 1,19</t>
+          <t>1,1; 1,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,69; 2,24</t>
+          <t>1,69; 1,8</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,29; 1,37</t>
+          <t>1,28; 1,37</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,38; 1,71</t>
+          <t>1,44; 1,53</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A_n_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P16A_n_R-Habitat-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según número de medicamentos consumidos por persona en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
+          <t>Población según el número de medicamentos consumidos por persona en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
